--- a/data/satisfaction_detail/2026/1-6月/酒店餐饮客户.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/酒店餐饮客户.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.69</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.890000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>9.99</v>
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.65</v>
+        <v>9.66</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -576,10 +576,10 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>9.91</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="11">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>9.69</v>
+        <v>9.65</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -627,12 +627,8 @@
           <t>菜品分量</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>10</v>
-      </c>
+      <c r="B14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -640,12 +636,8 @@
           <t>供应速度</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>10</v>
-      </c>
+      <c r="B15" s="4" t="inlineStr"/>
+      <c r="C15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -653,12 +645,8 @@
           <t>菜品卫生</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>10</v>
-      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -667,10 +655,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>9.49</v>
+        <v>9.58</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>9.949999999999999</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="18">
@@ -680,10 +668,10 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.35</v>
+        <v>9.42</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="19">
@@ -719,10 +707,10 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>9.720000000000001</v>
+        <v>9.84</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.970000000000001</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="22">

--- a/data/satisfaction_detail/2026/1-6月/酒店餐饮客户.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/酒店餐饮客户.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="8">
@@ -611,20 +611,16 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>菜品口味口相</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>9.970000000000001</v>
-      </c>
+          <t>菜品分量</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>菜品分量</t>
+          <t>供应速度</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr"/>
@@ -633,99 +629,99 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>供应速度</t>
+          <t>菜品卫生</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr"/>
       <c r="C15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>菜品卫生</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>硬件设施</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>9.92</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>硬件设施</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>9.58</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>9.92</v>
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>标识标牌清晰</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>9.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>标识标牌清晰</t>
+          <t>宴会视听设备</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>9.42</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>宴会视听设备</t>
+          <t>园区停车方便</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>园区停车方便</t>
+          <t>交通便利，容易到达</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>8.84</v>
+        <v>9.84</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.67</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>交通便利，容易到达</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>9.84</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>9.94</v>
-      </c>
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>智慧场馆</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>智慧场馆</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr"/>
-      <c r="C22" s="3" t="inlineStr"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>杭州国博APP</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>杭州国博APP</t>
+          <t>寻车系统</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr"/>
@@ -734,7 +730,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>寻车系统</t>
+          <t>室内导航系统</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr"/>
@@ -743,20 +739,11 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>室内导航系统</t>
+          <t>云上看馆</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr"/>
       <c r="C25" s="4" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>云上看馆</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr"/>
-      <c r="C26" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
